--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_192_R20.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_192_R20.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0345</v>
+        <v>1.7986</v>
       </c>
       <c r="E2" t="n">
-        <v>1.3316</v>
+        <v>1.0957</v>
       </c>
       <c r="F2" t="n">
         <v>0.7029</v>
@@ -610,10 +610,10 @@
         <v>1.1598</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2399</v>
+        <v>0.004</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1142</v>
+        <v>-0.1217</v>
       </c>
       <c r="U2" t="n">
         <v>0.1256</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. MONEKE</t>
+          <t>C. MILLER-MCINTYRE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6017</v>
+        <v>1.395</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9676</v>
+        <v>3.9581</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3659</v>
+        <v>-2.5631</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.4578</v>
+        <v>3.1085</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.7791</v>
+        <v>-0.3948</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3213</v>
+        <v>3.5033</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4196</v>
+        <v>5.378</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1449</v>
+        <v>1.0251</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2747</v>
+        <v>4.3529</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.8774</v>
+        <v>-2.2695</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.924</v>
+        <v>-1.4199</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9534</v>
+        <v>-0.8497</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4639</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3816</v>
+        <v>0.3587</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.326</v>
+        <v>-0.1727</v>
       </c>
       <c r="U3" t="n">
-        <v>1.7076</v>
+        <v>0.5313</v>
       </c>
       <c r="V3" t="n">
-        <v>1.214</v>
+        <v>-1.6083</v>
       </c>
       <c r="W3" t="n">
-        <v>2.0336</v>
+        <v>1.0722</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8197</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. MILLER-MCINTYRE</t>
+          <t>D. MOTIEJUNAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2537</v>
+        <v>0.6596</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1193</v>
+        <v>1.1667</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.8655</v>
+        <v>-0.5071</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1085</v>
+        <v>0.5043</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3948</v>
+        <v>0.8522999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>3.5033</v>
+        <v>-0.348</v>
       </c>
       <c r="J4" t="n">
-        <v>5.378</v>
+        <v>1.1155</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0251</v>
+        <v>1.0419</v>
       </c>
       <c r="L4" t="n">
-        <v>4.3529</v>
+        <v>0.0736</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.2695</v>
+        <v>-0.6112</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4199</v>
+        <v>-0.1896</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8497</v>
+        <v>-0.4216</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8556</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2175</v>
+        <v>0.1553</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0114</v>
+        <v>0.0512</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2289</v>
+        <v>0.1041</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.6805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. MOTIEJUNAS</t>
+          <t>C. MONEKE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6089</v>
+        <v>0.6002999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0487</v>
+        <v>1.8063</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4398</v>
+        <v>-1.206</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5043</v>
+        <v>-1.4578</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8522999999999999</v>
+        <v>-1.7791</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.348</v>
+        <v>0.3213</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1155</v>
+        <v>1.4196</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0419</v>
+        <v>0.1449</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0736</v>
+        <v>1.2747</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6112</v>
+        <v>-2.8774</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1896</v>
+        <v>-1.924</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4216</v>
+        <v>-0.9534</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1046</v>
+        <v>0.3802</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0668</v>
+        <v>-0.4872</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1713</v>
+        <v>0.8673999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.0336</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.8197</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3144</v>
+        <v>-0.1121</v>
       </c>
       <c r="E6" t="n">
-        <v>4.0545</v>
+        <v>4.2904</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.3689</v>
+        <v>-4.4025</v>
       </c>
       <c r="G6" t="n">
         <v>-0.1268</v>
@@ -922,13 +922,13 @@
         <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1876</v>
+        <v>0.0147</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6563</v>
+        <v>-0.4204</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4687</v>
+        <v>0.4351</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. KALINIC</t>
+          <t>D. DAVIDOVAC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9239000000000001</v>
+        <v>-0.7796</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9649</v>
+        <v>0.2606</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.8888</v>
+        <v>-1.0402</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3611</v>
+        <v>-0.7089</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0371</v>
+        <v>-0.3409</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3982</v>
+        <v>-0.368</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8373</v>
+        <v>0.0168</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8571</v>
+        <v>0.0168</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9802999999999999</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4762</v>
+        <v>-0.7257</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8942</v>
+        <v>-0.3577</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5821</v>
+        <v>-0.368</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3233</v>
+        <v>-0.0707</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2873</v>
+        <v>0.2438</v>
       </c>
       <c r="U8" t="n">
-        <v>0.036</v>
+        <v>-0.3145</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. DAVIDOVAC</t>
+          <t>N. KALINIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0155</v>
+        <v>-1.1194</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0247</v>
+        <v>0.5678</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0402</v>
+        <v>-1.6871</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7089</v>
+        <v>0.3611</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3409</v>
+        <v>-0.0371</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.368</v>
+        <v>0.3982</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0168</v>
+        <v>1.8373</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0168</v>
+        <v>0.8571</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7257</v>
+        <v>-1.4762</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3577</v>
+        <v>-0.8942</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.368</v>
+        <v>-0.5821</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3066</v>
+        <v>0.1278</v>
       </c>
       <c r="T9" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.1098</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3145</v>
+        <v>0.2377</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7154</v>
+        <v>-2.2607</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9337</v>
+        <v>-0.5798</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7817</v>
+        <v>-1.6809</v>
       </c>
       <c r="G10" t="n">
         <v>-3.2495</v>
@@ -1234,13 +1234,13 @@
         <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.002</v>
+        <v>-0.5474</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4402</v>
+        <v>-0.0863</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5619</v>
+        <v>-0.461</v>
       </c>
       <c r="V10" t="n">
         <v>1.0722</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. OJELEYE</t>
+          <t>D. GRAHAM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.2968</v>
+        <v>-4.7871</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1152</v>
+        <v>-5.7273</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.1816</v>
+        <v>0.9402</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.221</v>
+        <v>-3.2754</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.0563</v>
+        <v>-0.2004</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.1647</v>
+        <v>-3.075</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.1784</v>
+        <v>-3.522</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.6497</v>
+        <v>-0.4502</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-3.0718</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.0426</v>
+        <v>0.2466</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.4066</v>
+        <v>0.2499</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.636</v>
+        <v>-0.0033</v>
       </c>
       <c r="P11" t="n">
-        <v>1.6237</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0215</v>
+        <v>-0.1199</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0633</v>
+        <v>0.1142</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0848</v>
+        <v>-0.2341</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. GRAHAM</t>
+          <t>S. OJELEYE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.4008</v>
+        <v>-5.29</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.2738</v>
+        <v>-2.2764</v>
       </c>
       <c r="F12" t="n">
-        <v>0.873</v>
+        <v>-3.0136</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.2754</v>
+        <v>-6.221</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2004</v>
+        <v>-4.0563</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.075</v>
+        <v>-2.1647</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.522</v>
+        <v>-2.1784</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4502</v>
+        <v>-1.6497</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.0718</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2466</v>
+        <v>-4.0426</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2499</v>
+        <v>-2.4066</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0033</v>
+        <v>-1.636</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7336</v>
+        <v>-0.0147</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4323</v>
+        <v>-0.098</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3014</v>
+        <v>0.0833</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.882</v>
+        <v>-5.7812</v>
       </c>
       <c r="E13" t="n">
         <v>-5.7091</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1729</v>
+        <v>-0.0721</v>
       </c>
       <c r="G13" t="n">
         <v>-1.372</v>
@@ -1468,13 +1468,13 @@
         <v>1.3917</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0154</v>
+        <v>0.0854</v>
       </c>
       <c r="T13" t="n">
         <v>0.0633</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0786</v>
+        <v>0.0222</v>
       </c>
       <c r="V13" t="n">
         <v>1.0722</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-16.6152</v>
+        <v>-16.2418</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.381499999999998</v>
+        <v>-2.008</v>
       </c>
       <c r="F14" t="n">
-        <v>-14.2335</v>
+        <v>-14.2336</v>
       </c>
       <c r="G14" t="n">
         <v>-12.5997</v>
@@ -1546,13 +1546,13 @@
         <v>11.5978</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0001999999999999467</v>
+        <v>0.3734</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.4717</v>
+        <v>-1.0983</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4716</v>
+        <v>1.4718</v>
       </c>
       <c r="V14" t="n">
         <v>-0.5361</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.6741</v>
+        <v>7.91</v>
       </c>
       <c r="E15" t="n">
-        <v>7.1986</v>
+        <v>7.4345</v>
       </c>
       <c r="F15" t="n">
         <v>0.4755</v>
@@ -1624,10 +1624,10 @@
         <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3224</v>
+        <v>0.5583</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0474</v>
+        <v>0.2833</v>
       </c>
       <c r="U15" t="n">
         <v>0.275</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.8333</v>
+        <v>5.338</v>
       </c>
       <c r="E16" t="n">
-        <v>5.5733</v>
+        <v>5.8092</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7401</v>
+        <v>-0.4712</v>
       </c>
       <c r="G16" t="n">
         <v>4.2414</v>
@@ -1702,13 +1702,13 @@
         <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4261</v>
+        <v>0.0786</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4481</v>
+        <v>-0.2122</v>
       </c>
       <c r="U16" t="n">
-        <v>0.022</v>
+        <v>0.2908</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1418</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.9604</v>
+        <v>2.8089</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6115</v>
+        <v>1.0217</v>
       </c>
       <c r="F17" t="n">
-        <v>1.349</v>
+        <v>1.7872</v>
       </c>
       <c r="G17" t="n">
         <v>1.5883</v>
@@ -1780,13 +1780,13 @@
         <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3747</v>
+        <v>0.2232</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3031</v>
+        <v>-0.2867</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0716</v>
+        <v>0.5098</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3943</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.502</v>
+        <v>2.6708</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.205</v>
+        <v>-0.4973</v>
       </c>
       <c r="F18" t="n">
-        <v>2.7071</v>
+        <v>3.1681</v>
       </c>
       <c r="G18" t="n">
         <v>1.2156</v>
@@ -1858,13 +1858,13 @@
         <v>1.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6234</v>
+        <v>0.5454</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1949</v>
+        <v>-0.4872</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5715</v>
+        <v>1.0326</v>
       </c>
       <c r="V18" t="n">
         <v>0.6778999999999999</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. KEY</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.4356</v>
+        <v>1.861</v>
       </c>
       <c r="E19" t="n">
-        <v>3.7159</v>
+        <v>0.1728</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2803</v>
+        <v>1.6882</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2696</v>
+        <v>1.0404</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6037</v>
+        <v>0.2508</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8733</v>
+        <v>0.7896</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2067</v>
+        <v>0.4614</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1833</v>
+        <v>-0.124</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0234</v>
+        <v>0.5854</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4762</v>
+        <v>0.579</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5796</v>
+        <v>0.3748</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8966</v>
+        <v>0.2042</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4639</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>2.4552</v>
+        <v>0.0679</v>
       </c>
       <c r="T19" t="n">
-        <v>1.9189</v>
+        <v>-0.2552</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5364</v>
+        <v>0.3231</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.214</v>
+        <v>2.1444</v>
       </c>
       <c r="W19" t="n">
-        <v>1.7501</v>
+        <v>2.2862</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.9641</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.1378</v>
+        <v>1.5031</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4727</v>
+        <v>1.5906</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3348</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="G20" t="n">
         <v>2.1317</v>
@@ -2014,13 +2014,13 @@
         <v>1.1598</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4577</v>
+        <v>-0.0925</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8215</v>
+        <v>-0.7035</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3637</v>
+        <v>0.6111</v>
       </c>
       <c r="V20" t="n">
         <v>-0.5361</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9464</v>
+        <v>0.5038</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4324</v>
+        <v>-0.7862</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3788</v>
+        <v>1.29</v>
       </c>
       <c r="G21" t="n">
         <v>-0.6245000000000001</v>
@@ -2092,13 +2092,13 @@
         <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6431</v>
+        <v>0.2005</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2636</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3796</v>
+        <v>0.2908</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2217</v>
+        <v>0.4678</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5349</v>
+        <v>-1.0264</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7566000000000001</v>
+        <v>1.4942</v>
       </c>
       <c r="G22" t="n">
-        <v>1.0404</v>
+        <v>0.7813</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2508</v>
+        <v>0.43</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7896</v>
+        <v>0.3513</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4614</v>
+        <v>0.1882</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.124</v>
+        <v>0.2017</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5854</v>
+        <v>-0.0134</v>
       </c>
       <c r="M22" t="n">
-        <v>0.579</v>
+        <v>0.5931</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3748</v>
+        <v>0.2283</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2042</v>
+        <v>0.3648</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5714</v>
+        <v>0.2948</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.963</v>
+        <v>-0.0549</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6084000000000001</v>
+        <v>0.3497</v>
       </c>
       <c r="V22" t="n">
-        <v>2.1444</v>
+        <v>-1.0722</v>
       </c>
       <c r="W22" t="n">
-        <v>2.2862</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>B. KEY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,40 +2203,40 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0746</v>
+        <v>0.1274</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2624</v>
+        <v>2.4184</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3369</v>
+        <v>-2.291</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7813</v>
+        <v>-0.2696</v>
       </c>
       <c r="H23" t="n">
-        <v>0.43</v>
+        <v>0.6037</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3513</v>
+        <v>-0.8733</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1882</v>
+        <v>1.2067</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2017</v>
+        <v>1.1833</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.0134</v>
+        <v>0.0234</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5931</v>
+        <v>-1.4762</v>
       </c>
       <c r="N23" t="n">
-        <v>0.2283</v>
+        <v>-0.5796</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3648</v>
+        <v>-0.8966</v>
       </c>
       <c r="P23" t="n">
         <v>0.4639</v>
@@ -2248,22 +2248,22 @@
         <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0984</v>
+        <v>1.147</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2908</v>
+        <v>0.6214</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1924</v>
+        <v>0.5256</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.7501</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0722</v>
+        <v>-2.9641</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5163</v>
+        <v>-0.5613</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0675</v>
+        <v>-0.1684</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5838</v>
+        <v>-0.3929</v>
       </c>
       <c r="G24" t="n">
         <v>-1.1757</v>
@@ -2326,13 +2326,13 @@
         <v>0.232</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4274</v>
+        <v>0.3824</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1889</v>
+        <v>-0.047</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2385</v>
+        <v>0.4294</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.1355</v>
+        <v>-0.8153</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1284</v>
+        <v>0.4822</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.2639</v>
+        <v>-1.2975</v>
       </c>
       <c r="G25" t="n">
         <v>-0.1235</v>
@@ -2404,13 +2404,13 @@
         <v>1.6237</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4037</v>
+        <v>-0.0835</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4402</v>
+        <v>-0.0863</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0365</v>
+        <v>0.0029</v>
       </c>
       <c r="V25" t="n">
         <v>-1.0722</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.5191</v>
+        <v>-2.0536</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.0996</v>
+        <v>-2.2176</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.4195</v>
+        <v>0.1639</v>
       </c>
       <c r="G26" t="n">
         <v>-0.7171</v>
@@ -2482,13 +2482,13 @@
         <v>1.1598</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.6423</v>
+        <v>-0.1768</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.0351</v>
+        <v>-0.1531</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.6071</v>
+        <v>-0.0237</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>16.61499999999999</v>
+        <v>19.7606</v>
       </c>
       <c r="E27" t="n">
-        <v>14.2336</v>
+        <v>14.2335</v>
       </c>
       <c r="F27" t="n">
-        <v>2.3815</v>
+        <v>5.526999999999999</v>
       </c>
       <c r="G27" t="n">
         <v>12.5998</v>
@@ -2539,10 +2539,10 @@
         <v>11.5701</v>
       </c>
       <c r="L27" t="n">
-        <v>8.196399999999999</v>
+        <v>8.196400000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>-7.166500000000001</v>
+        <v>-7.1665</v>
       </c>
       <c r="N27" t="n">
         <v>-2.6506</v>
@@ -2560,13 +2560,13 @@
         <v>15.0771</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.0001999999999996449</v>
+        <v>3.1453</v>
       </c>
       <c r="T27" t="n">
         <v>-1.4717</v>
       </c>
       <c r="U27" t="n">
-        <v>1.4717</v>
+        <v>4.617100000000001</v>
       </c>
       <c r="V27" t="n">
         <v>0.5361000000000002</v>
